--- a/tabtools/demo/demo_survtab.xlsx
+++ b/tabtools/demo/demo_survtab.xlsx
@@ -189,12 +189,22 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="15">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -203,35 +213,16 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <b/>
     </font>
     <font>
       <sz val="12"/>
-      <b/>
-      <name val="Arial"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <i/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
     </font>
@@ -240,23 +231,8 @@
       <name val="Times New Roman"/>
     </font>
     <font>
+      <b/>
       <sz val="14"/>
-      <name val="Times New Roman"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <b/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <b/>
       <name val="Times New Roman"/>
     </font>
   </fonts>
@@ -268,7 +244,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -278,200 +254,84 @@
     </border>
     <border/>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="medium"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="medium"/>
       <bottom style="medium"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -493,177 +353,177 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12" t="s">
+      <c r="C5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="A10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="13" t="s">
+      <c r="C10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="0"/>
@@ -693,327 +553,327 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="12" t="s">
+      <c r="E4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="12" t="s">
+      <c r="C5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="12" t="s">
+      <c r="C11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="12" t="s">
+      <c r="E12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="12" t="s">
+      <c r="E13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="12" t="s">
+      <c r="E14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="12" t="s">
+      <c r="E15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="16" t="s">
+      <c r="A16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="13" t="s">
+      <c r="C16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="0"/>
@@ -1043,138 +903,138 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="23" t="s">
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="31" t="s">
+      <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="22" t="s">
+      <c r="A3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="32" t="s">
+      <c r="C3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="22" t="s">
+      <c r="A4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="22" t="s">
+      <c r="A5" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="22" t="s">
+      <c r="A6" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="22" t="s">
+      <c r="A7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="36" t="s">
+      <c r="A8" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="33" t="s">
+      <c r="C8" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13" t="s">
         <v>1</v>
       </c>
     </row>

--- a/tabtools/demo/demo_survtab.xlsx
+++ b/tabtools/demo/demo_survtab.xlsx
@@ -244,7 +244,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -254,6 +254,27 @@
     </border>
     <border/>
     <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -262,7 +283,28 @@
     </border>
     <border>
       <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -285,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -295,15 +337,30 @@
       <alignment horizontal="general" vertical="bottom" wrapText="false"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="false"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -315,16 +372,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -353,19 +410,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -373,16 +430,16 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="11" t="s">
         <v>23</v>
       </c>
     </row>
@@ -390,16 +447,16 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>24</v>
       </c>
     </row>
@@ -407,16 +464,16 @@
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -424,16 +481,16 @@
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -441,16 +498,16 @@
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -458,16 +515,16 @@
       <c r="A7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -475,16 +532,16 @@
       <c r="A8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -492,16 +549,16 @@
       <c r="A9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -509,16 +566,16 @@
       <c r="A10" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="C10" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -553,22 +610,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -576,19 +633,19 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="11" t="s">
         <v>23</v>
       </c>
     </row>
@@ -596,19 +653,19 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>24</v>
       </c>
     </row>
@@ -616,19 +673,19 @@
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="E4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -636,19 +693,19 @@
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="C5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -656,19 +713,19 @@
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -676,19 +733,19 @@
       <c r="A7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -696,19 +753,19 @@
       <c r="A8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -716,19 +773,19 @@
       <c r="A9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -736,19 +793,19 @@
       <c r="A10" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -756,19 +813,19 @@
       <c r="A11" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="C11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -776,19 +833,19 @@
       <c r="A12" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="E12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -796,19 +853,19 @@
       <c r="A13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="E13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -816,19 +873,19 @@
       <c r="A14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="E14" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -836,19 +893,19 @@
       <c r="A15" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="E15" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -856,19 +913,19 @@
       <c r="A16" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="6" t="s">
+      <c r="C16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -903,138 +960,138 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="15" t="s">
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="20" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="A2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="A3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="12" t="s">
+      <c r="C3" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="A5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="10" t="s">
+      <c r="A6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="A8" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="13" t="s">
+      <c r="C8" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>1</v>
       </c>
     </row>

--- a/tabtools/demo/demo_survtab.xlsx
+++ b/tabtools/demo/demo_survtab.xlsx
@@ -44,52 +44,52 @@
     <t xml:space="preserve">  1460 days</t>
   </si>
   <si>
-    <t>Log-rank test: chi2(1) = 2.80, p = 0.094</t>
-  </si>
-  <si>
-    <t>SSRI (N=8934)</t>
-  </si>
-  <si>
-    <t>5699.0</t>
-  </si>
-  <si>
-    <t>(5617.0, 5760.0)</t>
+    <t>Log-rank test: chi2(1) = 196.10, p &lt; 0.001</t>
+  </si>
+  <si>
+    <t>SSRI (N=8929)</t>
+  </si>
+  <si>
+    <t>5862.0</t>
+  </si>
+  <si>
+    <t>(5814.0, 5914.0)</t>
   </si>
   <si>
     <t>99.9%</t>
   </si>
   <si>
-    <t>99.5%</t>
-  </si>
-  <si>
-    <t>99.0%</t>
-  </si>
-  <si>
-    <t>97.3%</t>
-  </si>
-  <si>
-    <t>SNRI (N=6066)</t>
-  </si>
-  <si>
-    <t>5660.0</t>
-  </si>
-  <si>
-    <t>(5574.0, 5729.0)</t>
-  </si>
-  <si>
-    <t>99.8%</t>
+    <t>99.7%</t>
+  </si>
+  <si>
+    <t>99.3%</t>
+  </si>
+  <si>
+    <t>98.0%</t>
+  </si>
+  <si>
+    <t>SNRI (N=6071)</t>
+  </si>
+  <si>
+    <t>5212.0</t>
+  </si>
+  <si>
+    <t>(5116.0, 5338.0)</t>
   </si>
   <si>
     <t>99.1%</t>
   </si>
   <si>
-    <t>97.5%</t>
+    <t>98.6%</t>
+  </si>
+  <si>
+    <t>96.3%</t>
   </si>
   <si>
     <t>p</t>
   </si>
   <si>
-    <t>0.094</t>
+    <t>&lt;0.001</t>
   </si>
   <si>
     <t>Survival probabilities estimated by Kaplan-Meier method.</t>
@@ -104,55 +104,55 @@
     <t>Number at risk</t>
   </si>
   <si>
-    <t>1448.87 (1447.02, 1450.72)</t>
-  </si>
-  <si>
-    <t>8,654</t>
-  </si>
-  <si>
-    <t>8,437</t>
-  </si>
-  <si>
-    <t>8,266</t>
-  </si>
-  <si>
-    <t>7,645</t>
-  </si>
-  <si>
-    <t>1449.75 (1447.55, 1451.96)</t>
-  </si>
-  <si>
-    <t>5,850</t>
-  </si>
-  <si>
-    <t>5,725</t>
-  </si>
-  <si>
-    <t>5,611</t>
-  </si>
-  <si>
-    <t>5,185</t>
+    <t>1452.56 (1451.11, 1454.01)</t>
+  </si>
+  <si>
+    <t>8,723</t>
+  </si>
+  <si>
+    <t>8,577</t>
+  </si>
+  <si>
+    <t>8,420</t>
+  </si>
+  <si>
+    <t>7,888</t>
+  </si>
+  <si>
+    <t>1444.17 (1441.38, 1446.97)</t>
+  </si>
+  <si>
+    <t>5,781</t>
+  </si>
+  <si>
+    <t>5,585</t>
+  </si>
+  <si>
+    <t>5,457</t>
+  </si>
+  <si>
+    <t>4,942</t>
   </si>
   <si>
     <t>Difference (SSRI - SNRI)</t>
   </si>
   <si>
-    <t>39.0</t>
-  </si>
-  <si>
-    <t>0.1 (-0.1, 0.2)</t>
-  </si>
-  <si>
-    <t>-0.1 (-0.3, 0.2)</t>
-  </si>
-  <si>
-    <t>-0.1 (-0.4, 0.2)</t>
-  </si>
-  <si>
-    <t>-0.2 (-0.8, 0.3)</t>
-  </si>
-  <si>
-    <t>-0.88 (-3.76, 1.99)</t>
+    <t>650.0</t>
+  </si>
+  <si>
+    <t>0.2 (0.1, 0.4)</t>
+  </si>
+  <si>
+    <t>0.6 (0.3, 0.8)</t>
+  </si>
+  <si>
+    <t>0.7 (0.3, 1.0)</t>
+  </si>
+  <si>
+    <t>1.7 (1.1, 2.2)</t>
+  </si>
+  <si>
+    <t>8.38 (5.24, 11.53)</t>
   </si>
   <si>
     <t>RMST = restricted mean survival time truncated at 1460 days.</t>
@@ -167,22 +167,22 @@
     <t>0.1%</t>
   </si>
   <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>2.0%</t>
   </si>
   <si>
     <t>0.9%</t>
   </si>
   <si>
-    <t>2.5%</t>
+    <t>1.4%</t>
+  </si>
+  <si>
+    <t>3.7%</t>
   </si>
 </sst>
 </file>
@@ -505,7 +505,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>1</v>
@@ -522,7 +522,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>1</v>
@@ -720,7 +720,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>41</v>
@@ -740,7 +740,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>42</v>
@@ -1021,7 +1021,7 @@
         <v>49</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>1</v>
@@ -1038,7 +1038,7 @@
         <v>50</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>1</v>

--- a/tabtools/demo/demo_survtab.xlsx
+++ b/tabtools/demo/demo_survtab.xlsx
@@ -47,7 +47,7 @@
     <t>Log-rank test: chi2(1) = 196.10, p &lt; 0.001</t>
   </si>
   <si>
-    <t>SSRI (N=8929)</t>
+    <t>SSRI (N=8,929)</t>
   </si>
   <si>
     <t>5862.0</t>
@@ -68,7 +68,7 @@
     <t>98.0%</t>
   </si>
   <si>
-    <t>SNRI (N=6071)</t>
+    <t>SNRI (N=6,071)</t>
   </si>
   <si>
     <t>5212.0</t>
